--- a/artfynd/A 8229-2026 artfynd.xlsx
+++ b/artfynd/A 8229-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65920901</v>
+        <v>118237492</v>
       </c>
       <c r="B2" t="n">
-        <v>111333</v>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219716</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Krusfrö</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Selinum carvifolia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brobymosse, Upl</t>
+          <t>Broby mosse, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>657451</v>
+        <v>657773</v>
       </c>
       <c r="R2" t="n">
-        <v>6642171</v>
+        <v>6642374</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2003-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter. Observatör Annika Vinnersten</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,81 +760,71 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Mora Aronsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116899506</v>
+        <v>117013620</v>
       </c>
       <c r="B3" t="n">
-        <v>57297</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89767</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>2045</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Slöjmussling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Pleurotus calyptratus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lindblad) Sacc.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Broby mosse, Funbo, Upl</t>
+          <t>Broby mosse, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>657607</v>
+        <v>657699</v>
       </c>
       <c r="R3" t="n">
-        <v>6642183</v>
+        <v>6642466</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,12 +848,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På död, nedfallen gren av asp i fint skogsbryn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,8 +867,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Dead branch  # Populus tremula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -895,15 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116899434</v>
+        <v>110257610</v>
       </c>
       <c r="B4" t="n">
-        <v>57637</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,49 +917,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Broby mosse, Funbo, Upl</t>
+          <t>Broby mosse, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>657910</v>
+        <v>657535</v>
       </c>
       <c r="R4" t="n">
-        <v>6642456</v>
+        <v>6642103</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,15 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116899501</v>
+        <v>118237438</v>
       </c>
       <c r="B5" t="n">
-        <v>57637</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,49 +1014,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Broby mosse, Funbo, Upl</t>
+          <t>Broby mosse, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>657607</v>
+        <v>657810</v>
       </c>
       <c r="R5" t="n">
-        <v>6642183</v>
+        <v>6642592</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,12 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,6 +1082,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1123,15 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116899500</v>
+        <v>118237604</v>
       </c>
       <c r="B6" t="n">
-        <v>57805</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,16 +1112,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1161,24 +1134,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Broby mosse, Funbo, Upl</t>
+          <t>Broby mosse, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>657607</v>
+        <v>657488</v>
       </c>
       <c r="R6" t="n">
-        <v>6642183</v>
+        <v>6642119</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,12 +1175,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,37 +1207,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118237562</v>
+        <v>118237558</v>
       </c>
       <c r="B7" t="n">
-        <v>57309</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102977</v>
+        <v>100090</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1277,7 +1242,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1286,13 +1251,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>657292</v>
+        <v>657598</v>
       </c>
       <c r="R7" t="n">
-        <v>6642541</v>
+        <v>6642394</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1348,15 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118237453</v>
+        <v>110257611</v>
       </c>
       <c r="B8" t="n">
-        <v>56251</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,26 +1324,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208255</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1392,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>657307</v>
+        <v>657462</v>
       </c>
       <c r="R8" t="n">
-        <v>6642557</v>
+        <v>6642361</v>
       </c>
       <c r="S8" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,12 +1382,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,15 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118237580</v>
+        <v>116899506</v>
       </c>
       <c r="B9" t="n">
-        <v>57831</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102990</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1492,24 +1447,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Broby mosse, Upl</t>
+          <t>Broby mosse, Funbo, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>657635</v>
+        <v>657607</v>
       </c>
       <c r="R9" t="n">
-        <v>6642148</v>
+        <v>6642183</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,12 +1491,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,37 +1523,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118237604</v>
+        <v>118237562</v>
       </c>
       <c r="B10" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1605,7 +1558,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1614,13 +1567,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>657488</v>
+        <v>657292</v>
       </c>
       <c r="R10" t="n">
-        <v>6642119</v>
+        <v>6642541</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1644,12 +1597,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,15 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118237584</v>
+        <v>118237611</v>
       </c>
       <c r="B11" t="n">
-        <v>57659</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1725,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>657889</v>
+        <v>657557</v>
       </c>
       <c r="R11" t="n">
-        <v>6642406</v>
+        <v>6642095</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1755,12 +1703,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1787,19 +1735,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118237588</v>
+        <v>116899500</v>
       </c>
       <c r="B12" t="n">
-        <v>57831</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1825,24 +1768,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Broby mosse, Upl</t>
+          <t>Broby mosse, Funbo, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>657457</v>
+        <v>657607</v>
       </c>
       <c r="R12" t="n">
-        <v>6642431</v>
+        <v>6642183</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1898,32 +1844,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118237581</v>
+        <v>118237580</v>
       </c>
       <c r="B13" t="n">
-        <v>57659</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1947,10 +1888,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>657680</v>
+        <v>657635</v>
       </c>
       <c r="R13" t="n">
-        <v>6642210</v>
+        <v>6642148</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2009,32 +1950,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118237602</v>
+        <v>118237588</v>
       </c>
       <c r="B14" t="n">
-        <v>57966</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2058,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>657360</v>
+        <v>657457</v>
       </c>
       <c r="R14" t="n">
-        <v>6642562</v>
+        <v>6642431</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2088,12 +2024,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,37 +2056,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118237587</v>
+        <v>118237579</v>
       </c>
       <c r="B15" t="n">
-        <v>57718</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103001</v>
+        <v>103008</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2169,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>657929</v>
+        <v>657539</v>
       </c>
       <c r="R15" t="n">
-        <v>6642483</v>
+        <v>6642537</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,15 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118237495</v>
+        <v>118237591</v>
       </c>
       <c r="B16" t="n">
-        <v>100107</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,37 +2173,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>103008</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Broby mosse, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>657691</v>
+        <v>657652</v>
       </c>
       <c r="R16" t="n">
-        <v>6642523</v>
+        <v>6642478</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2301,12 +2236,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2333,15 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118237438</v>
+        <v>116899501</v>
       </c>
       <c r="B17" t="n">
-        <v>90913</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,37 +2279,49 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5321</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Broby mosse, Upl</t>
+          <t>Broby mosse, Funbo, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>657810</v>
+        <v>657607</v>
       </c>
       <c r="R17" t="n">
-        <v>6642592</v>
+        <v>6642183</v>
       </c>
       <c r="S17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2403,12 +2345,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,7 +2359,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2436,15 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118237454</v>
+        <v>118237581</v>
       </c>
       <c r="B18" t="n">
-        <v>100107</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,37 +2388,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Broby mosse, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>657326</v>
+        <v>657680</v>
       </c>
       <c r="R18" t="n">
-        <v>6642561</v>
+        <v>6642210</v>
       </c>
       <c r="S18" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2506,12 +2451,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2538,15 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118237458</v>
+        <v>118237602</v>
       </c>
       <c r="B19" t="n">
-        <v>56272</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,16 +2494,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208260</v>
+        <v>103044</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2576,19 +2516,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Broby mosse, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>657382</v>
+        <v>657360</v>
       </c>
       <c r="R19" t="n">
-        <v>6642561</v>
+        <v>6642562</v>
       </c>
       <c r="S19" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2612,12 +2557,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,53 +2589,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118237496</v>
+        <v>118237563</v>
       </c>
       <c r="B20" t="n">
-        <v>104853</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221141</v>
+        <v>103055</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Broby mosse, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>657696</v>
+        <v>657351</v>
       </c>
       <c r="R20" t="n">
-        <v>6642519</v>
+        <v>6642537</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2714,12 +2663,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2746,15 +2695,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118237591</v>
+        <v>118237601</v>
       </c>
       <c r="B21" t="n">
-        <v>57623</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2762,31 +2706,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103008</v>
+        <v>103055</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2795,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>657652</v>
+        <v>657532</v>
       </c>
       <c r="R21" t="n">
-        <v>6642478</v>
+        <v>6642538</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2825,12 +2769,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2857,53 +2801,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118237436</v>
+        <v>118237603</v>
       </c>
       <c r="B22" t="n">
-        <v>100107</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>103055</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Broby mosse, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>657800</v>
+        <v>657250</v>
       </c>
       <c r="R22" t="n">
-        <v>6642588</v>
+        <v>6642569</v>
       </c>
       <c r="S22" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2927,12 +2875,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2956,6 +2904,1857 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118237453</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>657307</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6642557</v>
+      </c>
+      <c r="S23" t="n">
+        <v>46</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118237458</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>657382</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6642561</v>
+      </c>
+      <c r="S24" t="n">
+        <v>43</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>65920901</v>
+      </c>
+      <c r="B25" t="n">
+        <v>111480</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219716</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Krusfrö</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Selinum carvifolia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Brobymosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>657451</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6642171</v>
+      </c>
+      <c r="S25" t="n">
+        <v>100</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2003-01-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2003-12-31</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter. Observatör Annika Vinnersten</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Via Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118237466</v>
+      </c>
+      <c r="B26" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>657310</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6642539</v>
+      </c>
+      <c r="S26" t="n">
+        <v>35</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>118237496</v>
+      </c>
+      <c r="B27" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>657696</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6642519</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>118237436</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>657800</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6642588</v>
+      </c>
+      <c r="S28" t="n">
+        <v>62</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>118237454</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>657326</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6642561</v>
+      </c>
+      <c r="S29" t="n">
+        <v>45</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>118237495</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>657691</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6642523</v>
+      </c>
+      <c r="S30" t="n">
+        <v>7</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>118237494</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91966</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>657846</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6642426</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>110257620</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>657977</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6642326</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-12-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-12-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>118237586</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58039</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>657952</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6642636</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>118237587</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>657929</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6642483</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>118237599</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>657918</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6642558</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>116899434</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Broby mosse, Funbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>657910</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6642456</v>
+      </c>
+      <c r="S36" t="n">
+        <v>50</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>118237584</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>657889</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6642406</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>118237585</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>657945</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6642618</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>118237597</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>657849</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6642578</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>118237598</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Broby mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>657895</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6642607</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
